--- a/healthcare_forms/004_nurse_shift_report_checklist--healthcare_forms.xlsx
+++ b/healthcare_forms/004_nurse_shift_report_checklist--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lab_results</t>
+          <t>lab_results_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lab Results</t>
+          <t>Lab Results 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medication_administered</t>
+          <t>medication_administered_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medication Administered</t>
+          <t>Medication Administered 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>lab_results</t>
+          <t>lab_results_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lab Results</t>
+          <t>Lab Results 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>patient_status</t>
+          <t>patient_status_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Patient Status</t>
+          <t>Patient Status 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>patient_name</t>
+          <t>patient_name_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Patient Name</t>
+          <t>Patient Name 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'latex'}</t>
+          <t>latex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Latex'}</t>
+          <t>Latex</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'shellfish'}</t>
+          <t>shellfish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Shellfish'}</t>
+          <t>Shellfish</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'abnormal'}</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Abnormal'}</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'unstable'}</t>
+          <t>unstable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Unstable'}</t>
+          <t>Unstable</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Signature'}</t>
+          <t>Signature</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'90-100'}</t>
+          <t>90-100</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '90-100'}</t>
+          <t>90-100</t>
         </is>
       </c>
     </row>
@@ -1335,114 +1335,114 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'&lt;_90'}</t>
+          <t>&lt;_90</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '&lt; 90'}</t>
+          <t>&lt; 90</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>medication_administered_choices</t>
+          <t>medication_administered_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medication_administered_choices</t>
+          <t>medication_administered_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'penicillin'}</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Penicillin'}</t>
+          <t>Penicillin</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lab_results_choices</t>
+          <t>lab_results_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>lab_results_choices</t>
+          <t>lab_results_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'abnormal'}</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Abnormal'}</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>patient_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>patient_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'unstable'}</t>
+          <t>unstable</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Unstable'}</t>
+          <t>Unstable</t>
         </is>
       </c>
     </row>
